--- a/tabtools/demo/table1.xlsx
+++ b/tabtools/demo/table1.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="130" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="260" uniqueCount="36">
   <si>
     <t>Table 1. Characteristics by Vehicle Origin</t>
   </si>
@@ -127,10 +127,2178 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <fonts count="511">
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
+  <fonts count="1021">
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
     </font>
     <font>
       <sz val="11"/>
@@ -2309,7 +4477,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="365">
+  <borders count="729">
     <border>
       <left/>
       <right/>
@@ -4805,11 +6973,2499 @@
       <bottom style="medium"/>
       <diagonal style="none"/>
     </border>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="medium"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="medium"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="medium"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="medium"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="medium"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="medium"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="medium"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="medium"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="none"/>
+      <top style="medium"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="none"/>
+      <top style="medium"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="medium"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="medium"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="medium"/>
+      <top style="medium"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="medium"/>
+      <top style="medium"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="medium"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="medium"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="medium"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="medium"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="medium"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="medium"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="medium"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="medium"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="medium"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="medium"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="medium"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="medium"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="medium"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="medium"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="medium"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="medium"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="medium"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="medium"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="medium"/>
+      <diagonal style="none"/>
+    </border>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="medium"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="medium"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="medium"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="medium"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="medium"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="medium"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="medium"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="medium"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="none"/>
+      <top style="medium"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="none"/>
+      <top style="medium"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="medium"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="medium"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="medium"/>
+      <top style="medium"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="medium"/>
+      <top style="medium"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="medium"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="medium"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="medium"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="medium"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="medium"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="medium"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="medium"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="medium"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="medium"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="medium"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="medium"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="medium"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="medium"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="medium"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="medium"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="medium"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="medium"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="medium"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="medium"/>
+      <diagonal style="none"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="365">
+  <cellXfs count="729">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0"/>
@@ -6234,6 +10890,1432 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="510" fillId="0" borderId="364" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="365" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="366" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="367" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="368" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="369" xfId="0"/>
+    <xf numFmtId="0" fontId="511" fillId="0" borderId="370" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="512" fillId="0" borderId="371" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="513" fillId="0" borderId="372" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="514" fillId="0" borderId="373" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="515" fillId="0" borderId="374" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="516" fillId="0" borderId="375" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="517" fillId="0" borderId="376" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="518" fillId="0" borderId="377" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="519" fillId="0" borderId="378" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="520" fillId="0" borderId="379" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="522" fillId="0" borderId="380" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="524" fillId="0" borderId="381" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="526" fillId="0" borderId="382" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="528" fillId="0" borderId="383" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="530" fillId="0" borderId="384" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="531" fillId="0" borderId="385" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="532" fillId="0" borderId="386" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="533" fillId="0" borderId="387" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="534" fillId="0" borderId="388" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="535" fillId="0" borderId="389" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="536" fillId="0" borderId="390" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="537" fillId="0" borderId="391" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="538" fillId="0" borderId="392" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="539" fillId="0" borderId="393" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="541" fillId="0" borderId="394" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="543" fillId="0" borderId="395" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="544" fillId="0" borderId="396" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="545" fillId="0" borderId="397" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="546" fillId="0" borderId="398" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="547" fillId="0" borderId="399" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="548" fillId="0" borderId="400" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="549" fillId="0" borderId="401" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="551" fillId="0" borderId="402" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="553" fillId="0" borderId="403" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="554" fillId="0" borderId="404" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="555" fillId="0" borderId="405" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="556" fillId="0" borderId="406" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="557" fillId="0" borderId="407" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="558" fillId="0" borderId="408" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="559" fillId="0" borderId="409" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="561" fillId="0" borderId="410" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="563" fillId="0" borderId="411" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="564" fillId="0" borderId="412" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="565" fillId="0" borderId="413" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="566" fillId="0" borderId="414" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="567" fillId="0" borderId="415" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="568" fillId="0" borderId="416" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="569" fillId="0" borderId="417" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="571" fillId="0" borderId="418" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="573" fillId="0" borderId="419" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="574" fillId="0" borderId="420" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="575" fillId="0" borderId="421" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="576" fillId="0" borderId="422" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="577" fillId="0" borderId="423" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="578" fillId="0" borderId="424" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="579" fillId="0" borderId="425" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="580" fillId="0" borderId="426" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="581" fillId="0" borderId="427" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="582" fillId="0" borderId="428" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="583" fillId="0" borderId="429" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="584" fillId="0" borderId="430" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="585" fillId="0" borderId="431" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="586" fillId="0" borderId="432" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="587" fillId="0" borderId="433" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="588" fillId="0" borderId="434" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="589" fillId="0" borderId="435" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="590" fillId="0" borderId="436" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="591" fillId="0" borderId="437" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="592" fillId="0" borderId="438" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="593" fillId="0" borderId="439" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="594" fillId="0" borderId="440" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="595" fillId="0" borderId="441" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="596" fillId="0" borderId="442" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="597" fillId="0" borderId="443" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="598" fillId="0" borderId="444" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="599" fillId="0" borderId="445" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="600" fillId="0" borderId="446" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="601" fillId="0" borderId="447" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="602" fillId="0" borderId="448" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="603" fillId="0" borderId="449" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="604" fillId="0" borderId="450" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="605" fillId="0" borderId="451" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="606" fillId="0" borderId="452" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="607" fillId="0" borderId="453" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="608" fillId="0" borderId="454" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="609" fillId="0" borderId="455" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="610" fillId="0" borderId="456" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="611" fillId="0" borderId="457" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="612" fillId="0" borderId="458" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="613" fillId="0" borderId="459" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="614" fillId="0" borderId="460" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="615" fillId="0" borderId="461" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="616" fillId="0" borderId="462" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="617" fillId="0" borderId="463" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="618" fillId="0" borderId="464" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="619" fillId="0" borderId="465" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="620" fillId="0" borderId="466" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="621" fillId="0" borderId="467" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="622" fillId="0" borderId="468" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="623" fillId="0" borderId="469" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="624" fillId="0" borderId="470" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="625" fillId="0" borderId="471" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="626" fillId="0" borderId="472" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="627" fillId="0" borderId="473" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="628" fillId="0" borderId="474" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="629" fillId="0" borderId="475" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="630" fillId="0" borderId="476" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="631" fillId="0" borderId="477" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="632" fillId="0" borderId="478" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="633" fillId="0" borderId="479" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="634" fillId="0" borderId="480" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="635" fillId="0" borderId="481" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="637" fillId="0" borderId="482" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="639" fillId="0" borderId="483" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="641" fillId="0" borderId="484" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="643" fillId="0" borderId="485" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="645" fillId="0" borderId="486" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="647" fillId="0" borderId="487" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="649" fillId="0" borderId="488" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="651" fillId="0" borderId="489" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="653" fillId="0" borderId="490" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="655" fillId="0" borderId="491" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="657" fillId="0" borderId="492" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="659" fillId="0" borderId="493" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="661" fillId="0" borderId="494" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="663" fillId="0" borderId="495" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="665" fillId="0" borderId="496" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="667" fillId="0" borderId="497" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="669" fillId="0" borderId="498" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="671" fillId="0" borderId="499" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="673" fillId="0" borderId="500" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="675" fillId="0" borderId="501" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="677" fillId="0" borderId="502" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="679" fillId="0" borderId="503" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="681" fillId="0" borderId="504" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="683" fillId="0" borderId="505" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="685" fillId="0" borderId="506" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="687" fillId="0" borderId="507" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="689" fillId="0" borderId="508" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="691" fillId="0" borderId="509" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="693" fillId="0" borderId="510" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="695" fillId="0" borderId="511" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="697" fillId="0" borderId="512" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="699" fillId="0" borderId="513" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="701" fillId="0" borderId="514" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="703" fillId="0" borderId="515" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="705" fillId="0" borderId="516" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="707" fillId="0" borderId="517" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="709" fillId="0" borderId="518" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="711" fillId="0" borderId="519" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="713" fillId="0" borderId="520" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="715" fillId="0" borderId="521" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="717" fillId="0" borderId="522" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="719" fillId="0" borderId="523" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="721" fillId="0" borderId="524" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="723" fillId="0" borderId="525" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="725" fillId="0" borderId="526" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="727" fillId="0" borderId="527" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="729" fillId="0" borderId="528" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="731" fillId="0" borderId="529" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="733" fillId="0" borderId="530" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="735" fillId="0" borderId="531" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="737" fillId="0" borderId="532" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="739" fillId="0" borderId="533" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="741" fillId="0" borderId="534" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="743" fillId="0" borderId="535" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="745" fillId="0" borderId="536" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="747" fillId="0" borderId="537" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="749" fillId="0" borderId="538" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="751" fillId="0" borderId="539" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="753" fillId="0" borderId="540" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="755" fillId="0" borderId="541" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="757" fillId="0" borderId="542" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="759" fillId="0" borderId="543" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="761" fillId="0" borderId="544" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="763" fillId="0" borderId="545" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="765" fillId="0" borderId="546" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="547" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="548" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="549" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="550" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="551" xfId="0"/>
+    <xf numFmtId="0" fontId="766" fillId="0" borderId="552" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="767" fillId="0" borderId="553" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="768" fillId="0" borderId="554" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="769" fillId="0" borderId="555" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="770" fillId="0" borderId="556" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="771" fillId="0" borderId="557" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="772" fillId="0" borderId="558" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="773" fillId="0" borderId="559" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="774" fillId="0" borderId="560" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="775" fillId="0" borderId="561" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="777" fillId="0" borderId="562" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="779" fillId="0" borderId="563" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="781" fillId="0" borderId="564" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="783" fillId="0" borderId="565" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="785" fillId="0" borderId="566" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="786" fillId="0" borderId="567" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="787" fillId="0" borderId="568" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="788" fillId="0" borderId="569" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="789" fillId="0" borderId="570" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="790" fillId="0" borderId="571" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="791" fillId="0" borderId="572" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="792" fillId="0" borderId="573" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="793" fillId="0" borderId="574" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="794" fillId="0" borderId="575" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="796" fillId="0" borderId="576" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="798" fillId="0" borderId="577" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="799" fillId="0" borderId="578" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="800" fillId="0" borderId="579" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="801" fillId="0" borderId="580" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="802" fillId="0" borderId="581" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="803" fillId="0" borderId="582" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="804" fillId="0" borderId="583" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="806" fillId="0" borderId="584" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="808" fillId="0" borderId="585" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="809" fillId="0" borderId="586" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="810" fillId="0" borderId="587" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="811" fillId="0" borderId="588" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="812" fillId="0" borderId="589" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="813" fillId="0" borderId="590" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="814" fillId="0" borderId="591" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="816" fillId="0" borderId="592" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="818" fillId="0" borderId="593" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="819" fillId="0" borderId="594" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="820" fillId="0" borderId="595" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="821" fillId="0" borderId="596" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="822" fillId="0" borderId="597" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="823" fillId="0" borderId="598" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="824" fillId="0" borderId="599" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="826" fillId="0" borderId="600" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="828" fillId="0" borderId="601" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="829" fillId="0" borderId="602" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="830" fillId="0" borderId="603" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="831" fillId="0" borderId="604" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="832" fillId="0" borderId="605" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="833" fillId="0" borderId="606" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="834" fillId="0" borderId="607" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="835" fillId="0" borderId="608" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="836" fillId="0" borderId="609" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="837" fillId="0" borderId="610" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="838" fillId="0" borderId="611" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="839" fillId="0" borderId="612" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="840" fillId="0" borderId="613" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="841" fillId="0" borderId="614" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="842" fillId="0" borderId="615" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="843" fillId="0" borderId="616" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="844" fillId="0" borderId="617" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="845" fillId="0" borderId="618" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="846" fillId="0" borderId="619" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="847" fillId="0" borderId="620" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="848" fillId="0" borderId="621" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="849" fillId="0" borderId="622" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="850" fillId="0" borderId="623" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="851" fillId="0" borderId="624" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="852" fillId="0" borderId="625" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="853" fillId="0" borderId="626" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="854" fillId="0" borderId="627" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="855" fillId="0" borderId="628" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="856" fillId="0" borderId="629" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="857" fillId="0" borderId="630" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="858" fillId="0" borderId="631" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="859" fillId="0" borderId="632" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="860" fillId="0" borderId="633" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="861" fillId="0" borderId="634" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="862" fillId="0" borderId="635" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="863" fillId="0" borderId="636" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="864" fillId="0" borderId="637" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="865" fillId="0" borderId="638" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="866" fillId="0" borderId="639" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="867" fillId="0" borderId="640" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="868" fillId="0" borderId="641" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="869" fillId="0" borderId="642" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="870" fillId="0" borderId="643" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="871" fillId="0" borderId="644" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="872" fillId="0" borderId="645" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="873" fillId="0" borderId="646" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="874" fillId="0" borderId="647" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="875" fillId="0" borderId="648" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="876" fillId="0" borderId="649" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="877" fillId="0" borderId="650" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="878" fillId="0" borderId="651" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="879" fillId="0" borderId="652" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="880" fillId="0" borderId="653" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="881" fillId="0" borderId="654" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="882" fillId="0" borderId="655" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="883" fillId="0" borderId="656" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="884" fillId="0" borderId="657" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="885" fillId="0" borderId="658" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="886" fillId="0" borderId="659" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="887" fillId="0" borderId="660" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="888" fillId="0" borderId="661" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="889" fillId="0" borderId="662" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="890" fillId="0" borderId="663" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="892" fillId="0" borderId="664" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="894" fillId="0" borderId="665" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="896" fillId="0" borderId="666" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="898" fillId="0" borderId="667" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="900" fillId="0" borderId="668" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="902" fillId="0" borderId="669" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="904" fillId="0" borderId="670" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="906" fillId="0" borderId="671" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="908" fillId="0" borderId="672" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="910" fillId="0" borderId="673" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="912" fillId="0" borderId="674" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="914" fillId="0" borderId="675" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="916" fillId="0" borderId="676" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="918" fillId="0" borderId="677" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="920" fillId="0" borderId="678" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="922" fillId="0" borderId="679" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="924" fillId="0" borderId="680" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="926" fillId="0" borderId="681" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="928" fillId="0" borderId="682" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="930" fillId="0" borderId="683" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="932" fillId="0" borderId="684" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="934" fillId="0" borderId="685" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="936" fillId="0" borderId="686" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="938" fillId="0" borderId="687" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="940" fillId="0" borderId="688" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="942" fillId="0" borderId="689" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="944" fillId="0" borderId="690" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="946" fillId="0" borderId="691" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="948" fillId="0" borderId="692" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="950" fillId="0" borderId="693" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="952" fillId="0" borderId="694" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="954" fillId="0" borderId="695" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="956" fillId="0" borderId="696" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="958" fillId="0" borderId="697" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="960" fillId="0" borderId="698" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="962" fillId="0" borderId="699" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="964" fillId="0" borderId="700" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="966" fillId="0" borderId="701" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="968" fillId="0" borderId="702" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="970" fillId="0" borderId="703" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="972" fillId="0" borderId="704" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="974" fillId="0" borderId="705" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="976" fillId="0" borderId="706" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="978" fillId="0" borderId="707" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="980" fillId="0" borderId="708" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="982" fillId="0" borderId="709" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="984" fillId="0" borderId="710" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="986" fillId="0" borderId="711" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="988" fillId="0" borderId="712" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="990" fillId="0" borderId="713" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="992" fillId="0" borderId="714" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="994" fillId="0" borderId="715" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="996" fillId="0" borderId="716" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="998" fillId="0" borderId="717" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1000" fillId="0" borderId="718" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1002" fillId="0" borderId="719" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1004" fillId="0" borderId="720" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1006" fillId="0" borderId="721" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1008" fillId="0" borderId="722" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1010" fillId="0" borderId="723" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1012" fillId="0" borderId="724" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1014" fillId="0" borderId="725" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1016" fillId="0" borderId="726" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1018" fillId="0" borderId="727" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1020" fillId="0" borderId="728" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -6249,230 +12331,230 @@
   <dimension ref="A1:E13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="1.7109375" style="184" customWidth="true"/>
-    <col min="2" max="2" width="15.7109375" style="185" customWidth="true"/>
-    <col min="3" max="4" width="12.7109375" style="186" customWidth="true"/>
-    <col min="5" max="5" width="10.7109375" style="187" customWidth="true"/>
+    <col min="1" max="1" width="1.7109375" style="548" customWidth="true"/>
+    <col min="2" max="2" width="15.7109375" style="549" customWidth="true"/>
+    <col min="3" max="4" width="12.7109375" style="550" customWidth="true"/>
+    <col min="5" max="5" width="10.7109375" style="551" customWidth="true"/>
   </cols>
   <sheetData>
-    <row r="1" s="183" customFormat="true" ht="30" customHeight="true">
-      <c r="A1" s="300" t="s">
+    <row r="1" s="547" customFormat="true" ht="30" customHeight="true">
+      <c r="A1" s="664" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="301" t="s">
+      <c r="B1" s="665" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="302" t="s">
+      <c r="C1" s="666" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="303" t="s">
+      <c r="D1" s="667" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="304" t="s">
+      <c r="E1" s="668" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="305" t="s">
+      <c r="A2" s="669" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="306" t="s">
+      <c r="B2" s="670" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="307" t="s">
+      <c r="C2" s="671" t="s">
         <v>14</v>
       </c>
-      <c r="D2" s="308" t="s">
+      <c r="D2" s="672" t="s">
         <v>24</v>
       </c>
-      <c r="E2" s="309" t="s">
+      <c r="E2" s="673" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="310" t="s">
+      <c r="A3" s="674" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="311" t="s">
+      <c r="B3" s="675" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="312" t="s">
+      <c r="C3" s="676" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="313" t="s">
+      <c r="D3" s="677" t="s">
         <v>25</v>
       </c>
-      <c r="E3" s="314" t="s">
+      <c r="E3" s="678" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="315" t="s">
+      <c r="A4" s="679" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="316" t="s">
+      <c r="B4" s="680" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="317" t="s">
+      <c r="C4" s="681" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="318" t="s">
+      <c r="D4" s="682" t="s">
         <v>26</v>
       </c>
-      <c r="E4" s="319" t="s">
+      <c r="E4" s="683" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="320" t="s">
+      <c r="A5" s="684" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="321" t="s">
+      <c r="B5" s="685" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="322" t="s">
+      <c r="C5" s="686" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="323" t="s">
+      <c r="D5" s="687" t="s">
         <v>27</v>
       </c>
-      <c r="E5" s="324" t="s">
+      <c r="E5" s="688" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="325" t="s">
+      <c r="A6" s="689" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="326" t="s">
+      <c r="B6" s="690" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="327" t="s">
+      <c r="C6" s="691" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="328" t="s">
+      <c r="D6" s="692" t="s">
         <v>28</v>
       </c>
-      <c r="E6" s="329" t="s">
+      <c r="E6" s="693" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="330" t="s">
+      <c r="A7" s="694" t="s">
         <v>1</v>
       </c>
-      <c r="B7" s="331" t="s">
+      <c r="B7" s="695" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="332" t="s">
+      <c r="C7" s="696" t="s">
         <v>19</v>
       </c>
-      <c r="D7" s="333" t="s">
+      <c r="D7" s="697" t="s">
         <v>29</v>
       </c>
-      <c r="E7" s="334" t="s">
+      <c r="E7" s="698" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="335" t="s">
+      <c r="A8" s="699" t="s">
         <v>1</v>
       </c>
-      <c r="B8" s="336" t="s">
+      <c r="B8" s="700" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="337" t="s">
+      <c r="C8" s="701" t="s">
         <v>1</v>
       </c>
-      <c r="D8" s="338" t="s">
+      <c r="D8" s="702" t="s">
         <v>1</v>
       </c>
-      <c r="E8" s="339" t="s">
+      <c r="E8" s="703" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="340" t="s">
+      <c r="A9" s="704" t="s">
         <v>1</v>
       </c>
-      <c r="B9" s="341" t="s">
+      <c r="B9" s="705" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="342" t="s">
+      <c r="C9" s="706" t="s">
         <v>20</v>
       </c>
-      <c r="D9" s="343" t="s">
+      <c r="D9" s="707" t="s">
         <v>30</v>
       </c>
-      <c r="E9" s="344" t="s">
+      <c r="E9" s="708" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="345" t="s">
+      <c r="A10" s="709" t="s">
         <v>1</v>
       </c>
-      <c r="B10" s="346" t="s">
+      <c r="B10" s="710" t="s">
         <v>10</v>
       </c>
-      <c r="C10" s="347" t="s">
+      <c r="C10" s="711" t="s">
         <v>21</v>
       </c>
-      <c r="D10" s="348" t="s">
+      <c r="D10" s="712" t="s">
         <v>30</v>
       </c>
-      <c r="E10" s="349" t="s">
+      <c r="E10" s="713" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="350" t="s">
+      <c r="A11" s="714" t="s">
         <v>1</v>
       </c>
-      <c r="B11" s="351" t="s">
+      <c r="B11" s="715" t="s">
         <v>11</v>
       </c>
-      <c r="C11" s="352" t="s">
+      <c r="C11" s="716" t="s">
         <v>22</v>
       </c>
-      <c r="D11" s="353" t="s">
+      <c r="D11" s="717" t="s">
         <v>31</v>
       </c>
-      <c r="E11" s="354" t="s">
+      <c r="E11" s="718" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="355" t="s">
+      <c r="A12" s="719" t="s">
         <v>1</v>
       </c>
-      <c r="B12" s="356" t="s">
+      <c r="B12" s="720" t="s">
         <v>12</v>
       </c>
-      <c r="C12" s="357" t="s">
+      <c r="C12" s="721" t="s">
         <v>23</v>
       </c>
-      <c r="D12" s="358" t="s">
+      <c r="D12" s="722" t="s">
         <v>32</v>
       </c>
-      <c r="E12" s="359" t="s">
+      <c r="E12" s="723" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="360" t="s">
+      <c r="A13" s="724" t="s">
         <v>1</v>
       </c>
-      <c r="B13" s="361" t="s">
+      <c r="B13" s="725" t="s">
         <v>13</v>
       </c>
-      <c r="C13" s="362" t="s">
+      <c r="C13" s="726" t="s">
         <v>20</v>
       </c>
-      <c r="D13" s="363" t="s">
+      <c r="D13" s="727" t="s">
         <v>32</v>
       </c>
-      <c r="E13" s="364" t="s">
+      <c r="E13" s="728" t="s">
         <v>1</v>
       </c>
     </row>

--- a/tabtools/demo/table1.xlsx
+++ b/tabtools/demo/table1.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="260" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="325" uniqueCount="36">
   <si>
     <t>Table 1. Characteristics by Vehicle Origin</t>
   </si>
@@ -127,10 +127,1094 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <fonts count="1021">
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
+  <fonts count="1276">
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
     </font>
     <font>
       <sz val="11"/>
@@ -4477,7 +5561,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="729">
+  <borders count="911">
     <border>
       <left/>
       <right/>
@@ -9461,11 +10545,1255 @@
       <bottom style="medium"/>
       <diagonal style="none"/>
     </border>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="medium"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="medium"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="medium"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="medium"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="medium"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="medium"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="medium"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="medium"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="none"/>
+      <top style="medium"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="none"/>
+      <top style="medium"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="medium"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="medium"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="medium"/>
+      <top style="medium"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="medium"/>
+      <top style="medium"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="medium"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="medium"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="medium"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="medium"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="medium"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="medium"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="medium"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="medium"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="medium"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="medium"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="medium"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="medium"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="medium"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="medium"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="medium"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="medium"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="medium"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="medium"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="medium"/>
+      <diagonal style="none"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="729">
+  <cellXfs count="911">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0"/>
@@ -12316,6 +14644,719 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="1020" fillId="0" borderId="728" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="729" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="730" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="731" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="732" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="733" xfId="0"/>
+    <xf numFmtId="0" fontId="1021" fillId="0" borderId="734" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1022" fillId="0" borderId="735" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1023" fillId="0" borderId="736" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1024" fillId="0" borderId="737" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1025" fillId="0" borderId="738" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1026" fillId="0" borderId="739" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1027" fillId="0" borderId="740" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1028" fillId="0" borderId="741" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1029" fillId="0" borderId="742" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1030" fillId="0" borderId="743" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1032" fillId="0" borderId="744" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1034" fillId="0" borderId="745" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1036" fillId="0" borderId="746" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1038" fillId="0" borderId="747" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1040" fillId="0" borderId="748" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1041" fillId="0" borderId="749" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1042" fillId="0" borderId="750" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1043" fillId="0" borderId="751" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1044" fillId="0" borderId="752" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1045" fillId="0" borderId="753" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1046" fillId="0" borderId="754" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1047" fillId="0" borderId="755" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1048" fillId="0" borderId="756" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1049" fillId="0" borderId="757" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1051" fillId="0" borderId="758" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1053" fillId="0" borderId="759" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1054" fillId="0" borderId="760" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1055" fillId="0" borderId="761" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1056" fillId="0" borderId="762" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1057" fillId="0" borderId="763" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1058" fillId="0" borderId="764" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1059" fillId="0" borderId="765" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1061" fillId="0" borderId="766" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1063" fillId="0" borderId="767" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1064" fillId="0" borderId="768" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1065" fillId="0" borderId="769" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1066" fillId="0" borderId="770" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1067" fillId="0" borderId="771" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1068" fillId="0" borderId="772" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1069" fillId="0" borderId="773" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1071" fillId="0" borderId="774" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1073" fillId="0" borderId="775" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1074" fillId="0" borderId="776" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1075" fillId="0" borderId="777" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1076" fillId="0" borderId="778" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1077" fillId="0" borderId="779" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1078" fillId="0" borderId="780" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1079" fillId="0" borderId="781" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1081" fillId="0" borderId="782" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1083" fillId="0" borderId="783" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1084" fillId="0" borderId="784" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1085" fillId="0" borderId="785" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1086" fillId="0" borderId="786" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1087" fillId="0" borderId="787" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1088" fillId="0" borderId="788" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1089" fillId="0" borderId="789" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1090" fillId="0" borderId="790" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1091" fillId="0" borderId="791" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1092" fillId="0" borderId="792" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1093" fillId="0" borderId="793" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1094" fillId="0" borderId="794" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1095" fillId="0" borderId="795" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1096" fillId="0" borderId="796" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1097" fillId="0" borderId="797" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1098" fillId="0" borderId="798" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1099" fillId="0" borderId="799" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1100" fillId="0" borderId="800" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1101" fillId="0" borderId="801" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1102" fillId="0" borderId="802" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1103" fillId="0" borderId="803" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1104" fillId="0" borderId="804" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1105" fillId="0" borderId="805" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1106" fillId="0" borderId="806" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1107" fillId="0" borderId="807" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1108" fillId="0" borderId="808" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1109" fillId="0" borderId="809" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1110" fillId="0" borderId="810" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1111" fillId="0" borderId="811" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1112" fillId="0" borderId="812" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1113" fillId="0" borderId="813" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1114" fillId="0" borderId="814" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1115" fillId="0" borderId="815" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1116" fillId="0" borderId="816" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1117" fillId="0" borderId="817" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1118" fillId="0" borderId="818" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1119" fillId="0" borderId="819" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1120" fillId="0" borderId="820" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1121" fillId="0" borderId="821" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1122" fillId="0" borderId="822" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1123" fillId="0" borderId="823" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1124" fillId="0" borderId="824" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1125" fillId="0" borderId="825" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1126" fillId="0" borderId="826" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1127" fillId="0" borderId="827" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1128" fillId="0" borderId="828" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1129" fillId="0" borderId="829" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1130" fillId="0" borderId="830" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1131" fillId="0" borderId="831" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1132" fillId="0" borderId="832" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1133" fillId="0" borderId="833" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1134" fillId="0" borderId="834" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1135" fillId="0" borderId="835" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1136" fillId="0" borderId="836" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1137" fillId="0" borderId="837" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1138" fillId="0" borderId="838" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1139" fillId="0" borderId="839" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1140" fillId="0" borderId="840" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1141" fillId="0" borderId="841" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1142" fillId="0" borderId="842" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1143" fillId="0" borderId="843" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1144" fillId="0" borderId="844" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1145" fillId="0" borderId="845" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1147" fillId="0" borderId="846" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1149" fillId="0" borderId="847" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1151" fillId="0" borderId="848" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1153" fillId="0" borderId="849" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1155" fillId="0" borderId="850" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1157" fillId="0" borderId="851" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1159" fillId="0" borderId="852" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1161" fillId="0" borderId="853" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1163" fillId="0" borderId="854" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1165" fillId="0" borderId="855" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1167" fillId="0" borderId="856" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1169" fillId="0" borderId="857" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1171" fillId="0" borderId="858" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1173" fillId="0" borderId="859" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1175" fillId="0" borderId="860" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1177" fillId="0" borderId="861" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1179" fillId="0" borderId="862" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1181" fillId="0" borderId="863" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1183" fillId="0" borderId="864" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1185" fillId="0" borderId="865" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1187" fillId="0" borderId="866" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1189" fillId="0" borderId="867" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1191" fillId="0" borderId="868" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1193" fillId="0" borderId="869" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1195" fillId="0" borderId="870" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1197" fillId="0" borderId="871" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1199" fillId="0" borderId="872" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1201" fillId="0" borderId="873" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1203" fillId="0" borderId="874" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1205" fillId="0" borderId="875" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1207" fillId="0" borderId="876" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1209" fillId="0" borderId="877" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1211" fillId="0" borderId="878" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1213" fillId="0" borderId="879" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1215" fillId="0" borderId="880" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1217" fillId="0" borderId="881" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1219" fillId="0" borderId="882" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1221" fillId="0" borderId="883" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1223" fillId="0" borderId="884" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1225" fillId="0" borderId="885" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1227" fillId="0" borderId="886" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1229" fillId="0" borderId="887" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1231" fillId="0" borderId="888" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1233" fillId="0" borderId="889" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1235" fillId="0" borderId="890" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1237" fillId="0" borderId="891" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1239" fillId="0" borderId="892" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1241" fillId="0" borderId="893" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1243" fillId="0" borderId="894" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1245" fillId="0" borderId="895" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1247" fillId="0" borderId="896" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1249" fillId="0" borderId="897" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1251" fillId="0" borderId="898" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1253" fillId="0" borderId="899" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1255" fillId="0" borderId="900" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1257" fillId="0" borderId="901" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1259" fillId="0" borderId="902" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1261" fillId="0" borderId="903" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1263" fillId="0" borderId="904" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1265" fillId="0" borderId="905" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1267" fillId="0" borderId="906" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1269" fillId="0" borderId="907" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1271" fillId="0" borderId="908" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1273" fillId="0" borderId="909" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1275" fillId="0" borderId="910" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -12331,230 +15372,230 @@
   <dimension ref="A1:E13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="1.7109375" style="548" customWidth="true"/>
-    <col min="2" max="2" width="15.7109375" style="549" customWidth="true"/>
-    <col min="3" max="4" width="12.7109375" style="550" customWidth="true"/>
-    <col min="5" max="5" width="10.7109375" style="551" customWidth="true"/>
+    <col min="1" max="1" width="1.7109375" style="730" customWidth="true"/>
+    <col min="2" max="2" width="15.7109375" style="731" customWidth="true"/>
+    <col min="3" max="4" width="12.7109375" style="732" customWidth="true"/>
+    <col min="5" max="5" width="10.7109375" style="733" customWidth="true"/>
   </cols>
   <sheetData>
-    <row r="1" s="547" customFormat="true" ht="30" customHeight="true">
-      <c r="A1" s="664" t="s">
+    <row r="1" s="729" customFormat="true" ht="30" customHeight="true">
+      <c r="A1" s="846" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="665" t="s">
+      <c r="B1" s="847" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="666" t="s">
+      <c r="C1" s="848" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="667" t="s">
+      <c r="D1" s="849" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="668" t="s">
+      <c r="E1" s="850" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="669" t="s">
+      <c r="A2" s="851" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="670" t="s">
+      <c r="B2" s="852" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="671" t="s">
+      <c r="C2" s="853" t="s">
         <v>14</v>
       </c>
-      <c r="D2" s="672" t="s">
+      <c r="D2" s="854" t="s">
         <v>24</v>
       </c>
-      <c r="E2" s="673" t="s">
+      <c r="E2" s="855" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="674" t="s">
+      <c r="A3" s="856" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="675" t="s">
+      <c r="B3" s="857" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="676" t="s">
+      <c r="C3" s="858" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="677" t="s">
+      <c r="D3" s="859" t="s">
         <v>25</v>
       </c>
-      <c r="E3" s="678" t="s">
+      <c r="E3" s="860" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="679" t="s">
+      <c r="A4" s="861" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="680" t="s">
+      <c r="B4" s="862" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="681" t="s">
+      <c r="C4" s="863" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="682" t="s">
+      <c r="D4" s="864" t="s">
         <v>26</v>
       </c>
-      <c r="E4" s="683" t="s">
+      <c r="E4" s="865" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="684" t="s">
+      <c r="A5" s="866" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="685" t="s">
+      <c r="B5" s="867" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="686" t="s">
+      <c r="C5" s="868" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="687" t="s">
+      <c r="D5" s="869" t="s">
         <v>27</v>
       </c>
-      <c r="E5" s="688" t="s">
+      <c r="E5" s="870" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="689" t="s">
+      <c r="A6" s="871" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="690" t="s">
+      <c r="B6" s="872" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="691" t="s">
+      <c r="C6" s="873" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="692" t="s">
+      <c r="D6" s="874" t="s">
         <v>28</v>
       </c>
-      <c r="E6" s="693" t="s">
+      <c r="E6" s="875" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="694" t="s">
+      <c r="A7" s="876" t="s">
         <v>1</v>
       </c>
-      <c r="B7" s="695" t="s">
+      <c r="B7" s="877" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="696" t="s">
+      <c r="C7" s="878" t="s">
         <v>19</v>
       </c>
-      <c r="D7" s="697" t="s">
+      <c r="D7" s="879" t="s">
         <v>29</v>
       </c>
-      <c r="E7" s="698" t="s">
+      <c r="E7" s="880" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="699" t="s">
+      <c r="A8" s="881" t="s">
         <v>1</v>
       </c>
-      <c r="B8" s="700" t="s">
+      <c r="B8" s="882" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="701" t="s">
+      <c r="C8" s="883" t="s">
         <v>1</v>
       </c>
-      <c r="D8" s="702" t="s">
+      <c r="D8" s="884" t="s">
         <v>1</v>
       </c>
-      <c r="E8" s="703" t="s">
+      <c r="E8" s="885" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="704" t="s">
+      <c r="A9" s="886" t="s">
         <v>1</v>
       </c>
-      <c r="B9" s="705" t="s">
+      <c r="B9" s="887" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="706" t="s">
+      <c r="C9" s="888" t="s">
         <v>20</v>
       </c>
-      <c r="D9" s="707" t="s">
+      <c r="D9" s="889" t="s">
         <v>30</v>
       </c>
-      <c r="E9" s="708" t="s">
+      <c r="E9" s="890" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="709" t="s">
+      <c r="A10" s="891" t="s">
         <v>1</v>
       </c>
-      <c r="B10" s="710" t="s">
+      <c r="B10" s="892" t="s">
         <v>10</v>
       </c>
-      <c r="C10" s="711" t="s">
+      <c r="C10" s="893" t="s">
         <v>21</v>
       </c>
-      <c r="D10" s="712" t="s">
+      <c r="D10" s="894" t="s">
         <v>30</v>
       </c>
-      <c r="E10" s="713" t="s">
+      <c r="E10" s="895" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="714" t="s">
+      <c r="A11" s="896" t="s">
         <v>1</v>
       </c>
-      <c r="B11" s="715" t="s">
+      <c r="B11" s="897" t="s">
         <v>11</v>
       </c>
-      <c r="C11" s="716" t="s">
+      <c r="C11" s="898" t="s">
         <v>22</v>
       </c>
-      <c r="D11" s="717" t="s">
+      <c r="D11" s="899" t="s">
         <v>31</v>
       </c>
-      <c r="E11" s="718" t="s">
+      <c r="E11" s="900" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="719" t="s">
+      <c r="A12" s="901" t="s">
         <v>1</v>
       </c>
-      <c r="B12" s="720" t="s">
+      <c r="B12" s="902" t="s">
         <v>12</v>
       </c>
-      <c r="C12" s="721" t="s">
+      <c r="C12" s="903" t="s">
         <v>23</v>
       </c>
-      <c r="D12" s="722" t="s">
+      <c r="D12" s="904" t="s">
         <v>32</v>
       </c>
-      <c r="E12" s="723" t="s">
+      <c r="E12" s="905" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="724" t="s">
+      <c r="A13" s="906" t="s">
         <v>1</v>
       </c>
-      <c r="B13" s="725" t="s">
+      <c r="B13" s="907" t="s">
         <v>13</v>
       </c>
-      <c r="C13" s="726" t="s">
+      <c r="C13" s="908" t="s">
         <v>20</v>
       </c>
-      <c r="D13" s="727" t="s">
+      <c r="D13" s="909" t="s">
         <v>32</v>
       </c>
-      <c r="E13" s="728" t="s">
+      <c r="E13" s="910" t="s">
         <v>1</v>
       </c>
     </row>

--- a/tabtools/demo/table1.xlsx
+++ b/tabtools/demo/table1.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="325" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="390" uniqueCount="36">
   <si>
     <t>Table 1. Characteristics by Vehicle Origin</t>
   </si>
@@ -127,10 +127,1094 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <fonts count="1276">
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
+  <fonts count="1531">
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
     </font>
     <font>
       <sz val="11"/>
@@ -5561,7 +6645,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="911">
+  <borders count="1093">
     <border>
       <left/>
       <right/>
@@ -11789,11 +12873,1255 @@
       <bottom style="medium"/>
       <diagonal style="none"/>
     </border>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="medium"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="medium"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="medium"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="medium"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="medium"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="medium"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="medium"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="medium"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="none"/>
+      <top style="medium"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="none"/>
+      <top style="medium"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="medium"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="medium"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="medium"/>
+      <top style="medium"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="medium"/>
+      <top style="medium"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="medium"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="medium"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="medium"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="medium"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="medium"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="medium"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="medium"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="medium"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="medium"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="medium"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="medium"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="medium"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="medium"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="medium"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="medium"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="medium"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="medium"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="medium"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="none"/>
+      <bottom style="medium"/>
+      <diagonal style="none"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="911">
+  <cellXfs count="1093">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0"/>
@@ -15357,6 +17685,719 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="1275" fillId="0" borderId="910" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="911" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="912" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="913" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="914" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="915" xfId="0"/>
+    <xf numFmtId="0" fontId="1276" fillId="0" borderId="916" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1277" fillId="0" borderId="917" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1278" fillId="0" borderId="918" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1279" fillId="0" borderId="919" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1280" fillId="0" borderId="920" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1281" fillId="0" borderId="921" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1282" fillId="0" borderId="922" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1283" fillId="0" borderId="923" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1284" fillId="0" borderId="924" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1285" fillId="0" borderId="925" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1287" fillId="0" borderId="926" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1289" fillId="0" borderId="927" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1291" fillId="0" borderId="928" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1293" fillId="0" borderId="929" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1295" fillId="0" borderId="930" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1296" fillId="0" borderId="931" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1297" fillId="0" borderId="932" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1298" fillId="0" borderId="933" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1299" fillId="0" borderId="934" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1300" fillId="0" borderId="935" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1301" fillId="0" borderId="936" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1302" fillId="0" borderId="937" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1303" fillId="0" borderId="938" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1304" fillId="0" borderId="939" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1306" fillId="0" borderId="940" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1308" fillId="0" borderId="941" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1309" fillId="0" borderId="942" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1310" fillId="0" borderId="943" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1311" fillId="0" borderId="944" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1312" fillId="0" borderId="945" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1313" fillId="0" borderId="946" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1314" fillId="0" borderId="947" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1316" fillId="0" borderId="948" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1318" fillId="0" borderId="949" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1319" fillId="0" borderId="950" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1320" fillId="0" borderId="951" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1321" fillId="0" borderId="952" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1322" fillId="0" borderId="953" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1323" fillId="0" borderId="954" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1324" fillId="0" borderId="955" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1326" fillId="0" borderId="956" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1328" fillId="0" borderId="957" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1329" fillId="0" borderId="958" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1330" fillId="0" borderId="959" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1331" fillId="0" borderId="960" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1332" fillId="0" borderId="961" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1333" fillId="0" borderId="962" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1334" fillId="0" borderId="963" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1336" fillId="0" borderId="964" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1338" fillId="0" borderId="965" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1339" fillId="0" borderId="966" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1340" fillId="0" borderId="967" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1341" fillId="0" borderId="968" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1342" fillId="0" borderId="969" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1343" fillId="0" borderId="970" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1344" fillId="0" borderId="971" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1345" fillId="0" borderId="972" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1346" fillId="0" borderId="973" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1347" fillId="0" borderId="974" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1348" fillId="0" borderId="975" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1349" fillId="0" borderId="976" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1350" fillId="0" borderId="977" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1351" fillId="0" borderId="978" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1352" fillId="0" borderId="979" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1353" fillId="0" borderId="980" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1354" fillId="0" borderId="981" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1355" fillId="0" borderId="982" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1356" fillId="0" borderId="983" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1357" fillId="0" borderId="984" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1358" fillId="0" borderId="985" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1359" fillId="0" borderId="986" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1360" fillId="0" borderId="987" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1361" fillId="0" borderId="988" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1362" fillId="0" borderId="989" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1363" fillId="0" borderId="990" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1364" fillId="0" borderId="991" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1365" fillId="0" borderId="992" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1366" fillId="0" borderId="993" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1367" fillId="0" borderId="994" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1368" fillId="0" borderId="995" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1369" fillId="0" borderId="996" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1370" fillId="0" borderId="997" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1371" fillId="0" borderId="998" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1372" fillId="0" borderId="999" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1373" fillId="0" borderId="1000" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1374" fillId="0" borderId="1001" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1375" fillId="0" borderId="1002" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1376" fillId="0" borderId="1003" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1377" fillId="0" borderId="1004" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1378" fillId="0" borderId="1005" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1379" fillId="0" borderId="1006" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1380" fillId="0" borderId="1007" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1381" fillId="0" borderId="1008" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1382" fillId="0" borderId="1009" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1383" fillId="0" borderId="1010" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1384" fillId="0" borderId="1011" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1385" fillId="0" borderId="1012" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1386" fillId="0" borderId="1013" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1387" fillId="0" borderId="1014" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1388" fillId="0" borderId="1015" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1389" fillId="0" borderId="1016" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1390" fillId="0" borderId="1017" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1391" fillId="0" borderId="1018" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1392" fillId="0" borderId="1019" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1393" fillId="0" borderId="1020" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1394" fillId="0" borderId="1021" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1395" fillId="0" borderId="1022" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1396" fillId="0" borderId="1023" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1397" fillId="0" borderId="1024" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1398" fillId="0" borderId="1025" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1399" fillId="0" borderId="1026" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1400" fillId="0" borderId="1027" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1402" fillId="0" borderId="1028" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1404" fillId="0" borderId="1029" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1406" fillId="0" borderId="1030" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1408" fillId="0" borderId="1031" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1410" fillId="0" borderId="1032" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1412" fillId="0" borderId="1033" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1414" fillId="0" borderId="1034" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1416" fillId="0" borderId="1035" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1418" fillId="0" borderId="1036" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1420" fillId="0" borderId="1037" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1422" fillId="0" borderId="1038" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1424" fillId="0" borderId="1039" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1426" fillId="0" borderId="1040" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1428" fillId="0" borderId="1041" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1430" fillId="0" borderId="1042" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1432" fillId="0" borderId="1043" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1434" fillId="0" borderId="1044" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1436" fillId="0" borderId="1045" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1438" fillId="0" borderId="1046" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1440" fillId="0" borderId="1047" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1442" fillId="0" borderId="1048" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1444" fillId="0" borderId="1049" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1446" fillId="0" borderId="1050" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1448" fillId="0" borderId="1051" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1450" fillId="0" borderId="1052" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1452" fillId="0" borderId="1053" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1454" fillId="0" borderId="1054" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1456" fillId="0" borderId="1055" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1458" fillId="0" borderId="1056" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1460" fillId="0" borderId="1057" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1462" fillId="0" borderId="1058" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1464" fillId="0" borderId="1059" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1466" fillId="0" borderId="1060" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1468" fillId="0" borderId="1061" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1470" fillId="0" borderId="1062" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1472" fillId="0" borderId="1063" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1474" fillId="0" borderId="1064" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1476" fillId="0" borderId="1065" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1478" fillId="0" borderId="1066" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1480" fillId="0" borderId="1067" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1482" fillId="0" borderId="1068" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1484" fillId="0" borderId="1069" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1486" fillId="0" borderId="1070" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1488" fillId="0" borderId="1071" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1490" fillId="0" borderId="1072" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1492" fillId="0" borderId="1073" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1494" fillId="0" borderId="1074" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1496" fillId="0" borderId="1075" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1498" fillId="0" borderId="1076" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1500" fillId="0" borderId="1077" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1502" fillId="0" borderId="1078" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1504" fillId="0" borderId="1079" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1506" fillId="0" borderId="1080" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1508" fillId="0" borderId="1081" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1510" fillId="0" borderId="1082" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1512" fillId="0" borderId="1083" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1514" fillId="0" borderId="1084" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1516" fillId="0" borderId="1085" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1518" fillId="0" borderId="1086" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1520" fillId="0" borderId="1087" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1522" fillId="0" borderId="1088" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1524" fillId="0" borderId="1089" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1526" fillId="0" borderId="1090" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1528" fillId="0" borderId="1091" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1530" fillId="0" borderId="1092" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -15372,230 +18413,230 @@
   <dimension ref="A1:E13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="1.7109375" style="730" customWidth="true"/>
-    <col min="2" max="2" width="15.7109375" style="731" customWidth="true"/>
-    <col min="3" max="4" width="12.7109375" style="732" customWidth="true"/>
-    <col min="5" max="5" width="10.7109375" style="733" customWidth="true"/>
+    <col min="1" max="1" width="1.7109375" style="912" customWidth="true"/>
+    <col min="2" max="2" width="15.7109375" style="913" customWidth="true"/>
+    <col min="3" max="4" width="12.7109375" style="914" customWidth="true"/>
+    <col min="5" max="5" width="10.7109375" style="915" customWidth="true"/>
   </cols>
   <sheetData>
-    <row r="1" s="729" customFormat="true" ht="30" customHeight="true">
-      <c r="A1" s="846" t="s">
+    <row r="1" s="911" customFormat="true" ht="30" customHeight="true">
+      <c r="A1" s="1028" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="847" t="s">
+      <c r="B1" s="1029" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="848" t="s">
+      <c r="C1" s="1030" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="849" t="s">
+      <c r="D1" s="1031" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="850" t="s">
+      <c r="E1" s="1032" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="851" t="s">
+      <c r="A2" s="1033" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="852" t="s">
+      <c r="B2" s="1034" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="853" t="s">
+      <c r="C2" s="1035" t="s">
         <v>14</v>
       </c>
-      <c r="D2" s="854" t="s">
+      <c r="D2" s="1036" t="s">
         <v>24</v>
       </c>
-      <c r="E2" s="855" t="s">
+      <c r="E2" s="1037" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="856" t="s">
+      <c r="A3" s="1038" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="857" t="s">
+      <c r="B3" s="1039" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="858" t="s">
+      <c r="C3" s="1040" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="859" t="s">
+      <c r="D3" s="1041" t="s">
         <v>25</v>
       </c>
-      <c r="E3" s="860" t="s">
+      <c r="E3" s="1042" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="861" t="s">
+      <c r="A4" s="1043" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="862" t="s">
+      <c r="B4" s="1044" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="863" t="s">
+      <c r="C4" s="1045" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="864" t="s">
+      <c r="D4" s="1046" t="s">
         <v>26</v>
       </c>
-      <c r="E4" s="865" t="s">
+      <c r="E4" s="1047" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="866" t="s">
+      <c r="A5" s="1048" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="867" t="s">
+      <c r="B5" s="1049" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="868" t="s">
+      <c r="C5" s="1050" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="869" t="s">
+      <c r="D5" s="1051" t="s">
         <v>27</v>
       </c>
-      <c r="E5" s="870" t="s">
+      <c r="E5" s="1052" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="871" t="s">
+      <c r="A6" s="1053" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="872" t="s">
+      <c r="B6" s="1054" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="873" t="s">
+      <c r="C6" s="1055" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="874" t="s">
+      <c r="D6" s="1056" t="s">
         <v>28</v>
       </c>
-      <c r="E6" s="875" t="s">
+      <c r="E6" s="1057" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="876" t="s">
+      <c r="A7" s="1058" t="s">
         <v>1</v>
       </c>
-      <c r="B7" s="877" t="s">
+      <c r="B7" s="1059" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="878" t="s">
+      <c r="C7" s="1060" t="s">
         <v>19</v>
       </c>
-      <c r="D7" s="879" t="s">
+      <c r="D7" s="1061" t="s">
         <v>29</v>
       </c>
-      <c r="E7" s="880" t="s">
+      <c r="E7" s="1062" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="881" t="s">
+      <c r="A8" s="1063" t="s">
         <v>1</v>
       </c>
-      <c r="B8" s="882" t="s">
+      <c r="B8" s="1064" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="883" t="s">
+      <c r="C8" s="1065" t="s">
         <v>1</v>
       </c>
-      <c r="D8" s="884" t="s">
+      <c r="D8" s="1066" t="s">
         <v>1</v>
       </c>
-      <c r="E8" s="885" t="s">
+      <c r="E8" s="1067" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="886" t="s">
+      <c r="A9" s="1068" t="s">
         <v>1</v>
       </c>
-      <c r="B9" s="887" t="s">
+      <c r="B9" s="1069" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="888" t="s">
+      <c r="C9" s="1070" t="s">
         <v>20</v>
       </c>
-      <c r="D9" s="889" t="s">
+      <c r="D9" s="1071" t="s">
         <v>30</v>
       </c>
-      <c r="E9" s="890" t="s">
+      <c r="E9" s="1072" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="891" t="s">
+      <c r="A10" s="1073" t="s">
         <v>1</v>
       </c>
-      <c r="B10" s="892" t="s">
+      <c r="B10" s="1074" t="s">
         <v>10</v>
       </c>
-      <c r="C10" s="893" t="s">
+      <c r="C10" s="1075" t="s">
         <v>21</v>
       </c>
-      <c r="D10" s="894" t="s">
+      <c r="D10" s="1076" t="s">
         <v>30</v>
       </c>
-      <c r="E10" s="895" t="s">
+      <c r="E10" s="1077" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="896" t="s">
+      <c r="A11" s="1078" t="s">
         <v>1</v>
       </c>
-      <c r="B11" s="897" t="s">
+      <c r="B11" s="1079" t="s">
         <v>11</v>
       </c>
-      <c r="C11" s="898" t="s">
+      <c r="C11" s="1080" t="s">
         <v>22</v>
       </c>
-      <c r="D11" s="899" t="s">
+      <c r="D11" s="1081" t="s">
         <v>31</v>
       </c>
-      <c r="E11" s="900" t="s">
+      <c r="E11" s="1082" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="901" t="s">
+      <c r="A12" s="1083" t="s">
         <v>1</v>
       </c>
-      <c r="B12" s="902" t="s">
+      <c r="B12" s="1084" t="s">
         <v>12</v>
       </c>
-      <c r="C12" s="903" t="s">
+      <c r="C12" s="1085" t="s">
         <v>23</v>
       </c>
-      <c r="D12" s="904" t="s">
+      <c r="D12" s="1086" t="s">
         <v>32</v>
       </c>
-      <c r="E12" s="905" t="s">
+      <c r="E12" s="1087" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="906" t="s">
+      <c r="A13" s="1088" t="s">
         <v>1</v>
       </c>
-      <c r="B13" s="907" t="s">
+      <c r="B13" s="1089" t="s">
         <v>13</v>
       </c>
-      <c r="C13" s="908" t="s">
+      <c r="C13" s="1090" t="s">
         <v>20</v>
       </c>
-      <c r="D13" s="909" t="s">
+      <c r="D13" s="1091" t="s">
         <v>32</v>
       </c>
-      <c r="E13" s="910" t="s">
+      <c r="E13" s="1092" t="s">
         <v>1</v>
       </c>
     </row>
